--- a/gstdatabase/GSTR-1-2021-2022.xlsx
+++ b/gstdatabase/GSTR-1-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDC6B51-D42A-4C05-9E2E-B02584FB5B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285A9926-5778-4281-9FA8-0FCF4F14A6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,10 +179,10 @@
     <t>Gujarat</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1078,14 +1078,14 @@
       </c>
       <c r="T10" s="6">
         <f>U10-S10</f>
-        <v>35689</v>
+        <v>35690</v>
       </c>
       <c r="U10" s="5">
-        <v>54460</v>
+        <v>54461</v>
       </c>
       <c r="V10" s="7">
         <f>U10/R10</f>
-        <v>0.96529476408238502</v>
+        <v>0.9653124889219753</v>
       </c>
       <c r="W10" s="5">
         <v>59030</v>
@@ -1095,14 +1095,14 @@
       </c>
       <c r="Y10" s="6">
         <f>Z10-X10</f>
-        <v>36750</v>
+        <v>36751</v>
       </c>
       <c r="Z10" s="5">
-        <v>56460</v>
+        <v>56461</v>
       </c>
       <c r="AA10" s="7">
         <f>Z10/W10</f>
-        <v>0.95646281551753343</v>
+        <v>0.95647975605624258</v>
       </c>
       <c r="AB10" s="6">
         <v>93037</v>
@@ -1112,14 +1112,14 @@
       </c>
       <c r="AD10" s="6">
         <f>AE10-AC10</f>
-        <v>50417</v>
+        <v>50419</v>
       </c>
       <c r="AE10" s="5">
-        <v>88069</v>
+        <v>88071</v>
       </c>
       <c r="AF10" s="7">
         <f>AE10/AB10</f>
-        <v>0.94660188957081592</v>
+        <v>0.94662338639466015</v>
       </c>
       <c r="AG10" s="5">
         <v>60457</v>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="AI10" s="6">
         <f>AJ10-AH10</f>
-        <v>33552</v>
+        <v>33553</v>
       </c>
       <c r="AJ10" s="5">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="AK10" s="7">
         <f>AJ10/AG10</f>
-        <v>0.95120498866963299</v>
+        <v>0.95122152935143989</v>
       </c>
       <c r="AL10" s="5">
         <v>62407</v>
@@ -1146,14 +1146,14 @@
       </c>
       <c r="AN10" s="6">
         <f>AO10-AM10</f>
-        <v>15570</v>
+        <v>15572</v>
       </c>
       <c r="AO10" s="5">
-        <v>59255</v>
+        <v>59257</v>
       </c>
       <c r="AP10" s="7">
         <f>AO10/AL10</f>
-        <v>0.94949284535388656</v>
+        <v>0.94952489304084475</v>
       </c>
       <c r="AQ10" s="6">
         <v>99346</v>
@@ -1163,14 +1163,14 @@
       </c>
       <c r="AS10" s="6">
         <f>AT10-AR10</f>
-        <v>54389</v>
+        <v>54391</v>
       </c>
       <c r="AT10" s="5">
-        <v>93655</v>
+        <v>93657</v>
       </c>
       <c r="AU10" s="7">
         <f>AT10/AQ10</f>
-        <v>0.94271535844422527</v>
+        <v>0.94273549010528856</v>
       </c>
       <c r="AV10" s="5">
         <v>63719</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="BH10" s="6">
         <f>BI10-BG10</f>
-        <v>59412</v>
+        <v>59413</v>
       </c>
       <c r="BI10" s="5">
-        <v>97135</v>
+        <v>97136</v>
       </c>
       <c r="BJ10" s="7">
         <f>BI10/BF10</f>
-        <v>0.93153614515603123</v>
+        <v>0.93154573527437323</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="AD11" s="6">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>44754</v>
+        <v>44755</v>
       </c>
       <c r="AE11" s="5">
-        <v>90720</v>
+        <v>90721</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.9661959230621765</v>
+        <v>0.9662065733699704</v>
       </c>
       <c r="AG11" s="5">
         <v>43295</v>
@@ -1375,14 +1375,14 @@
       </c>
       <c r="AS11" s="6">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="AT11" s="5">
-        <v>92864</v>
+        <v>92865</v>
       </c>
       <c r="AU11" s="7">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.96933258178326132</v>
+        <v>0.96934301997870609</v>
       </c>
       <c r="AV11" s="5">
         <v>43808</v>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="AX11" s="6">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>16327</v>
+        <v>16328</v>
       </c>
       <c r="AY11" s="5">
-        <v>41695</v>
+        <v>41696</v>
       </c>
       <c r="AZ11" s="7">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.95176680058436813</v>
+        <v>0.95178962746530316</v>
       </c>
       <c r="BA11" s="5">
         <v>44164</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="BC11" s="6">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>15737</v>
+        <v>15739</v>
       </c>
       <c r="BD11" s="5">
-        <v>42470</v>
+        <v>42472</v>
       </c>
       <c r="BE11" s="7">
         <f t="shared" ref="BE11:BE47" si="21">BD11/BA11</f>
-        <v>0.96164296712254327</v>
+        <v>0.9616882528756453</v>
       </c>
       <c r="BF11" s="5">
         <v>97423</v>
@@ -1426,14 +1426,14 @@
       </c>
       <c r="BH11" s="6">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>48804</v>
+        <v>48807</v>
       </c>
       <c r="BI11" s="5">
-        <v>94245</v>
+        <v>94248</v>
       </c>
       <c r="BJ11" s="7">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.96737936626874554</v>
+        <v>0.9674101598185233</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="T12" s="6">
         <f t="shared" si="6"/>
-        <v>43227</v>
+        <v>43229</v>
       </c>
       <c r="U12" s="5">
-        <v>148950</v>
+        <v>148952</v>
       </c>
       <c r="V12" s="7">
         <f t="shared" si="7"/>
-        <v>0.93193933478489377</v>
+        <v>0.93195184823685462</v>
       </c>
       <c r="W12" s="5">
         <v>162180</v>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="Y12" s="6">
         <f t="shared" si="8"/>
-        <v>40680</v>
+        <v>40682</v>
       </c>
       <c r="Z12" s="5">
-        <v>151686</v>
+        <v>151688</v>
       </c>
       <c r="AA12" s="7">
         <f t="shared" si="9"/>
-        <v>0.93529411764705883</v>
+        <v>0.93530644962387466</v>
       </c>
       <c r="AB12" s="6">
         <v>327297</v>
@@ -1536,14 +1536,14 @@
       </c>
       <c r="AD12" s="6">
         <f t="shared" si="10"/>
-        <v>85956</v>
+        <v>85958</v>
       </c>
       <c r="AE12" s="5">
-        <v>312380</v>
+        <v>312382</v>
       </c>
       <c r="AF12" s="7">
         <f t="shared" si="11"/>
-        <v>0.95442365802314111</v>
+        <v>0.95442976868104501</v>
       </c>
       <c r="AG12" s="5">
         <v>160729</v>
@@ -1553,14 +1553,14 @@
       </c>
       <c r="AI12" s="6">
         <f t="shared" si="12"/>
-        <v>37724</v>
+        <v>37726</v>
       </c>
       <c r="AJ12" s="5">
-        <v>149543</v>
+        <v>149545</v>
       </c>
       <c r="AK12" s="7">
         <f t="shared" si="13"/>
-        <v>0.93040459406827647</v>
+        <v>0.93041703737346715</v>
       </c>
       <c r="AL12" s="5">
         <v>162572</v>
@@ -1570,14 +1570,14 @@
       </c>
       <c r="AN12" s="6">
         <f t="shared" si="14"/>
-        <v>16149</v>
+        <v>16151</v>
       </c>
       <c r="AO12" s="5">
-        <v>151705</v>
+        <v>151707</v>
       </c>
       <c r="AP12" s="7">
         <f t="shared" si="15"/>
-        <v>0.93315577098147284</v>
+        <v>0.93316807322294126</v>
       </c>
       <c r="AQ12" s="6">
         <v>333129</v>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="AS12" s="6">
         <f t="shared" si="16"/>
-        <v>98733</v>
+        <v>98735</v>
       </c>
       <c r="AT12" s="5">
-        <v>316288</v>
+        <v>316290</v>
       </c>
       <c r="AU12" s="7">
         <f t="shared" si="17"/>
-        <v>0.94944601040437793</v>
+        <v>0.94945201408463387</v>
       </c>
       <c r="AV12" s="5">
         <v>161987</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="AX12" s="6">
         <f t="shared" si="18"/>
-        <v>32306</v>
+        <v>32308</v>
       </c>
       <c r="AY12" s="5">
-        <v>150785</v>
+        <v>150787</v>
       </c>
       <c r="AZ12" s="7">
         <f t="shared" si="19"/>
-        <v>0.93084630248106326</v>
+        <v>0.93085864915085781</v>
       </c>
       <c r="BA12" s="5">
         <v>163270</v>
@@ -1621,14 +1621,14 @@
       </c>
       <c r="BC12" s="6">
         <f t="shared" si="20"/>
-        <v>30965</v>
+        <v>30967</v>
       </c>
       <c r="BD12" s="5">
-        <v>152892</v>
+        <v>152894</v>
       </c>
       <c r="BE12" s="7">
         <f t="shared" si="21"/>
-        <v>0.93643657744839837</v>
+        <v>0.93644882709622101</v>
       </c>
       <c r="BF12" s="5">
         <v>336608</v>
@@ -1638,14 +1638,14 @@
       </c>
       <c r="BH12" s="6">
         <f t="shared" si="22"/>
-        <v>91188</v>
+        <v>91190</v>
       </c>
       <c r="BI12" s="5">
-        <v>319835</v>
+        <v>319837</v>
       </c>
       <c r="BJ12" s="7">
         <f t="shared" si="23"/>
-        <v>0.95017052476471142</v>
+        <v>0.95017646639414388</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1926,14 +1926,14 @@
       </c>
       <c r="T14" s="6">
         <f t="shared" si="6"/>
-        <v>40333</v>
+        <v>40335</v>
       </c>
       <c r="U14" s="5">
-        <v>72429</v>
+        <v>72431</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="7"/>
-        <v>0.9187067150358964</v>
+        <v>0.91873208351302671</v>
       </c>
       <c r="W14" s="5">
         <v>80553</v>
@@ -1943,14 +1943,14 @@
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="8"/>
-        <v>38584</v>
+        <v>38586</v>
       </c>
       <c r="Z14" s="5">
-        <v>74216</v>
+        <v>74218</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="9"/>
-        <v>0.9213312974066763</v>
+        <v>0.92135612578054205</v>
       </c>
       <c r="AB14" s="6">
         <v>144082</v>
@@ -1960,14 +1960,14 @@
       </c>
       <c r="AD14" s="6">
         <f t="shared" si="10"/>
-        <v>66590</v>
+        <v>66593</v>
       </c>
       <c r="AE14" s="5">
-        <v>135275</v>
+        <v>135278</v>
       </c>
       <c r="AF14" s="7">
         <f t="shared" si="11"/>
-        <v>0.93887508502102968</v>
+        <v>0.93889590649768884</v>
       </c>
       <c r="AG14" s="5">
         <v>79635</v>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="AI14" s="6">
         <f t="shared" si="12"/>
-        <v>36588</v>
+        <v>36590</v>
       </c>
       <c r="AJ14" s="5">
-        <v>73462</v>
+        <v>73464</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" si="13"/>
-        <v>0.92248383248571608</v>
+        <v>0.9225089470710115</v>
       </c>
       <c r="AL14" s="5">
         <v>81274</v>
@@ -1994,14 +1994,14 @@
       </c>
       <c r="AN14" s="6">
         <f t="shared" si="14"/>
-        <v>16029</v>
+        <v>16031</v>
       </c>
       <c r="AO14" s="5">
-        <v>75082</v>
+        <v>75084</v>
       </c>
       <c r="AP14" s="7">
         <f t="shared" si="15"/>
-        <v>0.9238132736176391</v>
+        <v>0.92383788173339565</v>
       </c>
       <c r="AQ14" s="6">
         <v>148266</v>
@@ -2011,14 +2011,14 @@
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="16"/>
-        <v>68574</v>
+        <v>68576</v>
       </c>
       <c r="AT14" s="5">
-        <v>139147</v>
+        <v>139149</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="17"/>
-        <v>0.93849567668919376</v>
+        <v>0.93850916595848</v>
       </c>
       <c r="AV14" s="5">
         <v>81291</v>
@@ -2028,14 +2028,14 @@
       </c>
       <c r="AX14" s="6">
         <f t="shared" si="18"/>
-        <v>31972</v>
+        <v>31974</v>
       </c>
       <c r="AY14" s="5">
-        <v>75338</v>
+        <v>75340</v>
       </c>
       <c r="AZ14" s="7">
         <f t="shared" si="19"/>
-        <v>0.92676926104980872</v>
+        <v>0.92679386401938713</v>
       </c>
       <c r="BA14" s="5">
         <v>82359</v>
@@ -2045,14 +2045,14 @@
       </c>
       <c r="BC14" s="6">
         <f t="shared" si="20"/>
-        <v>31701</v>
+        <v>31703</v>
       </c>
       <c r="BD14" s="5">
-        <v>76624</v>
+        <v>76626</v>
       </c>
       <c r="BE14" s="7">
         <f t="shared" si="21"/>
-        <v>0.93036583737053635</v>
+        <v>0.93039012129821874</v>
       </c>
       <c r="BF14" s="5">
         <v>151377</v>
@@ -2062,14 +2062,14 @@
       </c>
       <c r="BH14" s="6">
         <f t="shared" si="22"/>
-        <v>71665</v>
+        <v>71666</v>
       </c>
       <c r="BI14" s="5">
-        <v>141684</v>
+        <v>141685</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="23"/>
-        <v>0.9359678154541311</v>
+        <v>0.9359744214775032</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="AD15" s="6">
         <f t="shared" si="10"/>
-        <v>141610</v>
+        <v>141611</v>
       </c>
       <c r="AE15" s="5">
-        <v>430041</v>
+        <v>430042</v>
       </c>
       <c r="AF15" s="7">
         <f t="shared" si="11"/>
-        <v>0.94629724983826458</v>
+        <v>0.94629945031972995</v>
       </c>
       <c r="AG15" s="5">
         <v>261808</v>
@@ -2223,14 +2223,14 @@
       </c>
       <c r="AS15" s="6">
         <f t="shared" si="16"/>
-        <v>147627</v>
+        <v>147629</v>
       </c>
       <c r="AT15" s="5">
-        <v>439656</v>
+        <v>439658</v>
       </c>
       <c r="AU15" s="7">
         <f t="shared" si="17"/>
-        <v>0.94699771465742477</v>
+        <v>0.94700202256048838</v>
       </c>
       <c r="AV15" s="5">
         <v>264802</v>
@@ -2240,14 +2240,14 @@
       </c>
       <c r="AX15" s="6">
         <f t="shared" si="18"/>
-        <v>66382</v>
+        <v>66383</v>
       </c>
       <c r="AY15" s="5">
-        <v>248008</v>
+        <v>248009</v>
       </c>
       <c r="AZ15" s="7">
         <f t="shared" si="19"/>
-        <v>0.93657902885929867</v>
+        <v>0.93658280526582127</v>
       </c>
       <c r="BA15" s="5">
         <v>267720</v>
@@ -2274,14 +2274,14 @@
       </c>
       <c r="BH15" s="6">
         <f t="shared" si="22"/>
-        <v>146478</v>
+        <v>146480</v>
       </c>
       <c r="BI15" s="5">
-        <v>448376</v>
+        <v>448378</v>
       </c>
       <c r="BJ15" s="7">
         <f t="shared" si="23"/>
-        <v>0.95418638700670777</v>
+        <v>0.95419064319520586</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2350,14 +2350,14 @@
       </c>
       <c r="T16" s="6">
         <f t="shared" si="6"/>
-        <v>139503</v>
+        <v>139504</v>
       </c>
       <c r="U16" s="5">
-        <v>369204</v>
+        <v>369205</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="7"/>
-        <v>0.91462290793424295</v>
+        <v>0.91462538521755499</v>
       </c>
       <c r="W16" s="5">
         <v>406853</v>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>131968</v>
+        <v>131969</v>
       </c>
       <c r="Z16" s="5">
-        <v>376718</v>
+        <v>376719</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="9"/>
-        <v>0.92593147893710992</v>
+        <v>0.92593393682730618</v>
       </c>
       <c r="AB16" s="6">
         <v>722282</v>
@@ -2384,14 +2384,14 @@
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>196122</v>
+        <v>196124</v>
       </c>
       <c r="AE16" s="5">
-        <v>689382</v>
+        <v>689384</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" si="11"/>
-        <v>0.95444992399090656</v>
+        <v>0.95445269299248769</v>
       </c>
       <c r="AG16" s="5">
         <v>397671</v>
@@ -2401,14 +2401,14 @@
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="12"/>
-        <v>116375</v>
+        <v>116376</v>
       </c>
       <c r="AJ16" s="5">
-        <v>374285</v>
+        <v>374286</v>
       </c>
       <c r="AK16" s="7">
         <f t="shared" si="13"/>
-        <v>0.94119259387785381</v>
+        <v>0.94119510851935395</v>
       </c>
       <c r="AL16" s="5">
         <v>400740</v>
@@ -2418,14 +2418,14 @@
       </c>
       <c r="AN16" s="6">
         <f t="shared" si="14"/>
-        <v>48229</v>
+        <v>48230</v>
       </c>
       <c r="AO16" s="5">
-        <v>380509</v>
+        <v>380510</v>
       </c>
       <c r="AP16" s="7">
         <f t="shared" si="15"/>
-        <v>0.94951589559315264</v>
+        <v>0.94951839097669311</v>
       </c>
       <c r="AQ16" s="6">
         <v>730568</v>
@@ -2435,14 +2435,14 @@
       </c>
       <c r="AS16" s="6">
         <f t="shared" si="16"/>
-        <v>198857</v>
+        <v>198861</v>
       </c>
       <c r="AT16" s="5">
-        <v>699694</v>
+        <v>699698</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="17"/>
-        <v>0.95773973127758127</v>
+        <v>0.9577452064694868</v>
       </c>
       <c r="AV16" s="5">
         <v>402711</v>
@@ -2452,14 +2452,14 @@
       </c>
       <c r="AX16" s="6">
         <f t="shared" si="18"/>
-        <v>96443</v>
+        <v>96445</v>
       </c>
       <c r="AY16" s="5">
-        <v>378364</v>
+        <v>378366</v>
       </c>
       <c r="AZ16" s="7">
         <f t="shared" si="19"/>
-        <v>0.93954225238446432</v>
+        <v>0.93954721872509073</v>
       </c>
       <c r="BA16" s="5">
         <v>402569</v>
@@ -2469,14 +2469,14 @@
       </c>
       <c r="BC16" s="6">
         <f t="shared" si="20"/>
-        <v>94068</v>
+        <v>94069</v>
       </c>
       <c r="BD16" s="5">
-        <v>384277</v>
+        <v>384278</v>
       </c>
       <c r="BE16" s="7">
         <f t="shared" si="21"/>
-        <v>0.95456182666822331</v>
+        <v>0.95456431071443648</v>
       </c>
       <c r="BF16" s="5">
         <v>736680</v>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>196448</v>
+        <v>196451</v>
       </c>
       <c r="BI16" s="5">
-        <v>706647</v>
+        <v>706650</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.95923195960254115</v>
+        <v>0.95923603192702389</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="T17" s="6">
         <f t="shared" si="6"/>
-        <v>119513</v>
+        <v>119514</v>
       </c>
       <c r="U17" s="5">
-        <v>253307</v>
+        <v>253308</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="7"/>
-        <v>0.96973351249746376</v>
+        <v>0.96973734079084883</v>
       </c>
       <c r="W17" s="5">
         <v>269820</v>
@@ -2579,14 +2579,14 @@
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="8"/>
-        <v>114749</v>
+        <v>114751</v>
       </c>
       <c r="Z17" s="5">
-        <v>262478</v>
+        <v>262480</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="9"/>
-        <v>0.9727892669186865</v>
+        <v>0.97279667926765989</v>
       </c>
       <c r="AB17" s="6">
         <v>613565</v>
@@ -2596,14 +2596,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>238284</v>
+        <v>238287</v>
       </c>
       <c r="AE17" s="5">
-        <v>597235</v>
+        <v>597238</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.97338505292837763</v>
+        <v>0.97338994238589227</v>
       </c>
       <c r="AG17" s="5">
         <v>263808</v>
@@ -2613,14 +2613,14 @@
       </c>
       <c r="AI17" s="6">
         <f t="shared" si="12"/>
-        <v>102915</v>
+        <v>102917</v>
       </c>
       <c r="AJ17" s="5">
-        <v>255227</v>
+        <v>255229</v>
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="13"/>
-        <v>0.96747255579815628</v>
+        <v>0.96748013706938374</v>
       </c>
       <c r="AL17" s="5">
         <v>270212</v>
@@ -2630,14 +2630,14 @@
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="14"/>
-        <v>46325</v>
+        <v>46327</v>
       </c>
       <c r="AO17" s="5">
-        <v>262877</v>
+        <v>262879</v>
       </c>
       <c r="AP17" s="7">
         <f t="shared" si="15"/>
-        <v>0.97285464746199279</v>
+        <v>0.97286204905777685</v>
       </c>
       <c r="AQ17" s="6">
         <v>633137</v>
@@ -2647,14 +2647,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>253914</v>
+        <v>253919</v>
       </c>
       <c r="AT17" s="5">
-        <v>612917</v>
+        <v>612922</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.96806378398356119</v>
+        <v>0.96807168116853071</v>
       </c>
       <c r="AV17" s="5">
         <v>270996</v>
@@ -2664,14 +2664,14 @@
       </c>
       <c r="AX17" s="6">
         <f t="shared" si="18"/>
-        <v>84234</v>
+        <v>84237</v>
       </c>
       <c r="AY17" s="5">
-        <v>261441</v>
+        <v>261444</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="19"/>
-        <v>0.96474117699154227</v>
+        <v>0.96475224726564235</v>
       </c>
       <c r="BA17" s="5">
         <v>277009</v>
@@ -2681,14 +2681,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>81165</v>
+        <v>81169</v>
       </c>
       <c r="BD17" s="5">
-        <v>270960</v>
+        <v>270964</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.97816316437372075</v>
+        <v>0.97817760433776524</v>
       </c>
       <c r="BF17" s="5">
         <v>651560</v>
@@ -2698,14 +2698,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>264509</v>
+        <v>264514</v>
       </c>
       <c r="BI17" s="5">
-        <v>629121</v>
+        <v>629126</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.96556111486279084</v>
+        <v>0.96556878875314633</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2774,14 +2774,14 @@
       </c>
       <c r="T18" s="6">
         <f t="shared" si="6"/>
-        <v>411981</v>
+        <v>411983</v>
       </c>
       <c r="U18" s="5">
-        <v>732695</v>
+        <v>732697</v>
       </c>
       <c r="V18" s="7">
         <f t="shared" si="7"/>
-        <v>0.94480944429042091</v>
+        <v>0.94481202328835134</v>
       </c>
       <c r="W18" s="5">
         <v>789854</v>
@@ -2791,14 +2791,14 @@
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="8"/>
-        <v>390055</v>
+        <v>390057</v>
       </c>
       <c r="Z18" s="5">
-        <v>748181</v>
+        <v>748183</v>
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="9"/>
-        <v>0.94723961643544252</v>
+        <v>0.94724214854897237</v>
       </c>
       <c r="AB18" s="6">
         <v>1245422</v>
@@ -2808,14 +2808,14 @@
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="10"/>
-        <v>569102</v>
+        <v>569106</v>
       </c>
       <c r="AE18" s="5">
-        <v>1175176</v>
+        <v>1175180</v>
       </c>
       <c r="AF18" s="7">
         <f t="shared" si="11"/>
-        <v>0.94359662829145463</v>
+        <v>0.9435998400542146</v>
       </c>
       <c r="AG18" s="5">
         <v>794310</v>
@@ -2825,14 +2825,14 @@
       </c>
       <c r="AI18" s="6">
         <f t="shared" si="12"/>
-        <v>388025</v>
+        <v>388028</v>
       </c>
       <c r="AJ18" s="5">
-        <v>750384</v>
+        <v>750387</v>
       </c>
       <c r="AK18" s="7">
         <f t="shared" si="13"/>
-        <v>0.94469917286701666</v>
+        <v>0.94470294972995428</v>
       </c>
       <c r="AL18" s="5">
         <v>807429</v>
@@ -2842,14 +2842,14 @@
       </c>
       <c r="AN18" s="6">
         <f t="shared" si="14"/>
-        <v>142069</v>
+        <v>142071</v>
       </c>
       <c r="AO18" s="5">
-        <v>765809</v>
+        <v>765811</v>
       </c>
       <c r="AP18" s="7">
         <f t="shared" si="15"/>
-        <v>0.94845367208757669</v>
+        <v>0.94845614908555431</v>
       </c>
       <c r="AQ18" s="6">
         <v>1285494</v>
@@ -2859,14 +2859,14 @@
       </c>
       <c r="AS18" s="6">
         <f t="shared" si="16"/>
-        <v>603857</v>
+        <v>603860</v>
       </c>
       <c r="AT18" s="5">
-        <v>1212047</v>
+        <v>1212050</v>
       </c>
       <c r="AU18" s="7">
         <f t="shared" si="17"/>
-        <v>0.94286476638552963</v>
+        <v>0.94286710011870922</v>
       </c>
       <c r="AV18" s="5">
         <v>820095</v>
@@ -2876,14 +2876,14 @@
       </c>
       <c r="AX18" s="6">
         <f t="shared" si="18"/>
-        <v>349475</v>
+        <v>349477</v>
       </c>
       <c r="AY18" s="5">
-        <v>773543</v>
+        <v>773545</v>
       </c>
       <c r="AZ18" s="7">
         <f t="shared" si="19"/>
-        <v>0.94323584462775656</v>
+        <v>0.94323828336960958</v>
       </c>
       <c r="BA18" s="5">
         <v>829968</v>
@@ -2893,14 +2893,14 @@
       </c>
       <c r="BC18" s="6">
         <f t="shared" si="20"/>
-        <v>340743</v>
+        <v>340745</v>
       </c>
       <c r="BD18" s="5">
-        <v>785696</v>
+        <v>785698</v>
       </c>
       <c r="BE18" s="7">
         <f t="shared" si="21"/>
-        <v>0.94665818441192917</v>
+        <v>0.94666059414338866</v>
       </c>
       <c r="BF18" s="5">
         <v>1319511</v>
@@ -2910,14 +2910,14 @@
       </c>
       <c r="BH18" s="6">
         <f t="shared" si="22"/>
-        <v>631901</v>
+        <v>631904</v>
       </c>
       <c r="BI18" s="5">
-        <v>1235575</v>
+        <v>1235578</v>
       </c>
       <c r="BJ18" s="7">
         <f t="shared" si="23"/>
-        <v>0.93638855606357208</v>
+        <v>0.93639082963309894</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="T19" s="6">
         <f t="shared" si="6"/>
-        <v>158289</v>
+        <v>158290</v>
       </c>
       <c r="U19" s="5">
-        <v>216801</v>
+        <v>216802</v>
       </c>
       <c r="V19" s="7">
         <f t="shared" si="7"/>
-        <v>0.85198080694156808</v>
+        <v>0.85198473672421182</v>
       </c>
       <c r="W19" s="5">
         <v>263449</v>
@@ -3003,14 +3003,14 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="8"/>
-        <v>162776</v>
+        <v>162777</v>
       </c>
       <c r="Z19" s="5">
-        <v>229841</v>
+        <v>229842</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="9"/>
-        <v>0.87243071714069897</v>
+        <v>0.87243451294178376</v>
       </c>
       <c r="AB19" s="6">
         <v>418128</v>
@@ -3020,14 +3020,14 @@
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="10"/>
-        <v>231558</v>
+        <v>231560</v>
       </c>
       <c r="AE19" s="5">
-        <v>372446</v>
+        <v>372448</v>
       </c>
       <c r="AF19" s="7">
         <f t="shared" si="11"/>
-        <v>0.8907463743159989</v>
+        <v>0.89075115754027478</v>
       </c>
       <c r="AG19" s="5">
         <v>259213</v>
@@ -3037,14 +3037,14 @@
       </c>
       <c r="AI19" s="6">
         <f t="shared" si="12"/>
-        <v>162939</v>
+        <v>162940</v>
       </c>
       <c r="AJ19" s="5">
-        <v>221045</v>
+        <v>221046</v>
       </c>
       <c r="AK19" s="7">
         <f t="shared" si="13"/>
-        <v>0.85275429858841956</v>
+        <v>0.85275815641962405</v>
       </c>
       <c r="AL19" s="5">
         <v>262802</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="AN19" s="6">
         <f t="shared" si="14"/>
-        <v>63219</v>
+        <v>63220</v>
       </c>
       <c r="AO19" s="5">
-        <v>224993</v>
+        <v>224994</v>
       </c>
       <c r="AP19" s="7">
         <f t="shared" si="15"/>
-        <v>0.85613123187799178</v>
+        <v>0.85613503702407134</v>
       </c>
       <c r="AQ19" s="6">
         <v>437396</v>
@@ -3071,14 +3071,14 @@
       </c>
       <c r="AS19" s="6">
         <f t="shared" si="16"/>
-        <v>254091</v>
+        <v>254092</v>
       </c>
       <c r="AT19" s="5">
-        <v>381174</v>
+        <v>381175</v>
       </c>
       <c r="AU19" s="7">
         <f t="shared" si="17"/>
-        <v>0.87146201611354468</v>
+        <v>0.87146430237130657</v>
       </c>
       <c r="AV19" s="5">
         <v>265429</v>
@@ -3088,14 +3088,14 @@
       </c>
       <c r="AX19" s="6">
         <f t="shared" si="18"/>
-        <v>145067</v>
+        <v>145068</v>
       </c>
       <c r="AY19" s="5">
-        <v>226871</v>
+        <v>226872</v>
       </c>
       <c r="AZ19" s="7">
         <f t="shared" si="19"/>
-        <v>0.85473328083969724</v>
+        <v>0.85473704832554087</v>
       </c>
       <c r="BA19" s="5">
         <v>272122</v>
@@ -3105,14 +3105,14 @@
       </c>
       <c r="BC19" s="6">
         <f t="shared" si="20"/>
-        <v>142889</v>
+        <v>142890</v>
       </c>
       <c r="BD19" s="5">
-        <v>232939</v>
+        <v>232940</v>
       </c>
       <c r="BE19" s="7">
         <f t="shared" si="21"/>
-        <v>0.85600943694372378</v>
+        <v>0.85601311176604611</v>
       </c>
       <c r="BF19" s="5">
         <v>456786</v>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="BH19" s="6">
         <f t="shared" si="22"/>
-        <v>273308</v>
+        <v>273309</v>
       </c>
       <c r="BI19" s="5">
-        <v>393756</v>
+        <v>393757</v>
       </c>
       <c r="BJ19" s="7">
         <f t="shared" si="23"/>
-        <v>0.8620141598034966</v>
+        <v>0.86201634901244784</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3410,14 +3410,14 @@
       </c>
       <c r="T21" s="6">
         <f t="shared" si="6"/>
-        <v>5832</v>
+        <v>5833</v>
       </c>
       <c r="U21" s="5">
-        <v>7504</v>
+        <v>7505</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="7"/>
-        <v>0.73302725407834324</v>
+        <v>0.73312493894695707</v>
       </c>
       <c r="W21" s="5">
         <v>10162</v>
@@ -3427,14 +3427,14 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="8"/>
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="Z21" s="5">
-        <v>7610</v>
+        <v>7611</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="9"/>
-        <v>0.74886833300531397</v>
+        <v>0.74896673883093878</v>
       </c>
       <c r="AB21" s="6">
         <v>13196</v>
@@ -3444,14 +3444,14 @@
       </c>
       <c r="AD21" s="6">
         <f t="shared" si="10"/>
-        <v>7182</v>
+        <v>7183</v>
       </c>
       <c r="AE21" s="5">
-        <v>10282</v>
+        <v>10283</v>
       </c>
       <c r="AF21" s="7">
         <f t="shared" si="11"/>
-        <v>0.77917550772961508</v>
+        <v>0.77925128826917245</v>
       </c>
       <c r="AG21" s="5">
         <v>10295</v>
@@ -3461,14 +3461,14 @@
       </c>
       <c r="AI21" s="6">
         <f t="shared" si="12"/>
-        <v>5357</v>
+        <v>5358</v>
       </c>
       <c r="AJ21" s="5">
-        <v>7692</v>
+        <v>7693</v>
       </c>
       <c r="AK21" s="7">
         <f t="shared" si="13"/>
-        <v>0.74715881495871783</v>
+        <v>0.7472559494900437</v>
       </c>
       <c r="AL21" s="5">
         <v>10459</v>
@@ -3478,14 +3478,14 @@
       </c>
       <c r="AN21" s="6">
         <f t="shared" si="14"/>
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="AO21" s="5">
-        <v>7786</v>
+        <v>7787</v>
       </c>
       <c r="AP21" s="7">
         <f t="shared" si="15"/>
-        <v>0.74443063390381492</v>
+        <v>0.74452624533894252</v>
       </c>
       <c r="AQ21" s="6">
         <v>13595</v>
@@ -3495,14 +3495,14 @@
       </c>
       <c r="AS21" s="6">
         <f t="shared" si="16"/>
-        <v>7431</v>
+        <v>7432</v>
       </c>
       <c r="AT21" s="5">
-        <v>10594</v>
+        <v>10595</v>
       </c>
       <c r="AU21" s="7">
         <f t="shared" si="17"/>
-        <v>0.77925707980875325</v>
+        <v>0.7793306362633321</v>
       </c>
       <c r="AV21" s="5">
         <v>10391</v>
@@ -3512,14 +3512,14 @@
       </c>
       <c r="AX21" s="6">
         <f t="shared" si="18"/>
-        <v>5189</v>
+        <v>5190</v>
       </c>
       <c r="AY21" s="5">
-        <v>7910</v>
+        <v>7911</v>
       </c>
       <c r="AZ21" s="7">
         <f t="shared" si="19"/>
-        <v>0.76123568472716774</v>
+        <v>0.76133192185545184</v>
       </c>
       <c r="BA21" s="5">
         <v>10525</v>
@@ -3529,14 +3529,14 @@
       </c>
       <c r="BC21" s="6">
         <f t="shared" si="20"/>
-        <v>5275</v>
+        <v>5276</v>
       </c>
       <c r="BD21" s="5">
-        <v>8050</v>
+        <v>8051</v>
       </c>
       <c r="BE21" s="7">
         <f t="shared" si="21"/>
-        <v>0.76484560570071258</v>
+        <v>0.76494061757719711</v>
       </c>
       <c r="BF21" s="5">
         <v>13618</v>
@@ -3546,14 +3546,14 @@
       </c>
       <c r="BH21" s="6">
         <f t="shared" si="22"/>
-        <v>8336</v>
+        <v>8337</v>
       </c>
       <c r="BI21" s="5">
-        <v>10969</v>
+        <v>10970</v>
       </c>
       <c r="BJ21" s="7">
         <f t="shared" si="23"/>
-        <v>0.80547804376560439</v>
+        <v>0.80555147598766341</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3834,14 +3834,14 @@
       </c>
       <c r="T23" s="6">
         <f t="shared" si="6"/>
-        <v>5226</v>
+        <v>5227</v>
       </c>
       <c r="U23" s="5">
-        <v>6634</v>
+        <v>6635</v>
       </c>
       <c r="V23" s="7">
         <f t="shared" si="7"/>
-        <v>0.69284595300261098</v>
+        <v>0.69295039164490857</v>
       </c>
       <c r="W23" s="5">
         <v>9750</v>
@@ -3868,14 +3868,14 @@
       </c>
       <c r="AD23" s="6">
         <f t="shared" si="10"/>
-        <v>5998</v>
+        <v>5999</v>
       </c>
       <c r="AE23" s="5">
-        <v>8194</v>
+        <v>8195</v>
       </c>
       <c r="AF23" s="7">
         <f t="shared" si="11"/>
-        <v>0.71650926897516609</v>
+        <v>0.71659671213711085</v>
       </c>
       <c r="AG23" s="5">
         <v>9837</v>
@@ -3919,14 +3919,14 @@
       </c>
       <c r="AS23" s="6">
         <f t="shared" si="16"/>
-        <v>6301</v>
+        <v>6302</v>
       </c>
       <c r="AT23" s="5">
-        <v>8477</v>
+        <v>8478</v>
       </c>
       <c r="AU23" s="7">
         <f t="shared" si="17"/>
-        <v>0.80198675496688743</v>
+        <v>0.80208136234626304</v>
       </c>
       <c r="AV23" s="5">
         <v>8848</v>
@@ -4258,14 +4258,14 @@
       </c>
       <c r="T25" s="6">
         <f t="shared" si="6"/>
-        <v>9362</v>
+        <v>9363</v>
       </c>
       <c r="U25" s="5">
-        <v>16018</v>
+        <v>16019</v>
       </c>
       <c r="V25" s="7">
         <f t="shared" si="7"/>
-        <v>0.87324865071144309</v>
+        <v>0.87330316742081449</v>
       </c>
       <c r="W25" s="5">
         <v>18513</v>
@@ -4275,14 +4275,14 @@
       </c>
       <c r="Y25" s="6">
         <f t="shared" si="8"/>
-        <v>8967</v>
+        <v>8968</v>
       </c>
       <c r="Z25" s="5">
-        <v>16212</v>
+        <v>16213</v>
       </c>
       <c r="AA25" s="7">
         <f t="shared" si="9"/>
-        <v>0.87570896127045861</v>
+        <v>0.87576297736725539</v>
       </c>
       <c r="AB25" s="6">
         <v>25418</v>
@@ -4292,14 +4292,14 @@
       </c>
       <c r="AD25" s="6">
         <f t="shared" si="10"/>
-        <v>11224</v>
+        <v>11225</v>
       </c>
       <c r="AE25" s="5">
-        <v>23124</v>
+        <v>23125</v>
       </c>
       <c r="AF25" s="7">
         <f t="shared" si="11"/>
-        <v>0.90974899677393972</v>
+        <v>0.90978833897238176</v>
       </c>
       <c r="AG25" s="5">
         <v>18377</v>
@@ -4309,14 +4309,14 @@
       </c>
       <c r="AI25" s="6">
         <f t="shared" si="12"/>
-        <v>8043</v>
+        <v>8044</v>
       </c>
       <c r="AJ25" s="5">
-        <v>16262</v>
+        <v>16263</v>
       </c>
       <c r="AK25" s="7">
         <f t="shared" si="13"/>
-        <v>0.88491048593350385</v>
+        <v>0.88496490177939813</v>
       </c>
       <c r="AL25" s="5">
         <v>18561</v>
@@ -4326,14 +4326,14 @@
       </c>
       <c r="AN25" s="6">
         <f t="shared" si="14"/>
-        <v>3263</v>
+        <v>3265</v>
       </c>
       <c r="AO25" s="5">
-        <v>16436</v>
+        <v>16438</v>
       </c>
       <c r="AP25" s="7">
         <f t="shared" si="15"/>
-        <v>0.88551263401756375</v>
+        <v>0.88562038683260602</v>
       </c>
       <c r="AQ25" s="6">
         <v>25768</v>
@@ -4343,14 +4343,14 @@
       </c>
       <c r="AS25" s="6">
         <f t="shared" si="16"/>
-        <v>11307</v>
+        <v>11309</v>
       </c>
       <c r="AT25" s="5">
-        <v>23459</v>
+        <v>23461</v>
       </c>
       <c r="AU25" s="7">
         <f t="shared" si="17"/>
-        <v>0.91039273517541142</v>
+        <v>0.91047035082272587</v>
       </c>
       <c r="AV25" s="5">
         <v>18472</v>
@@ -4360,14 +4360,14 @@
       </c>
       <c r="AX25" s="6">
         <f t="shared" si="18"/>
-        <v>7575</v>
+        <v>7577</v>
       </c>
       <c r="AY25" s="5">
-        <v>16636</v>
+        <v>16638</v>
       </c>
       <c r="AZ25" s="7">
         <f t="shared" si="19"/>
-        <v>0.90060632308358601</v>
+        <v>0.90071459506279772</v>
       </c>
       <c r="BA25" s="5">
         <v>18607</v>
@@ -4377,14 +4377,14 @@
       </c>
       <c r="BC25" s="6">
         <f t="shared" si="20"/>
-        <v>7699</v>
+        <v>7701</v>
       </c>
       <c r="BD25" s="5">
-        <v>16937</v>
+        <v>16939</v>
       </c>
       <c r="BE25" s="7">
         <f t="shared" si="21"/>
-        <v>0.91024883108507548</v>
+        <v>0.91035631751491375</v>
       </c>
       <c r="BF25" s="5">
         <v>26131</v>
@@ -4394,14 +4394,14 @@
       </c>
       <c r="BH25" s="6">
         <f t="shared" si="22"/>
-        <v>13562</v>
+        <v>13564</v>
       </c>
       <c r="BI25" s="5">
-        <v>24027</v>
+        <v>24029</v>
       </c>
       <c r="BJ25" s="7">
         <f t="shared" si="23"/>
-        <v>0.91948260686540895</v>
+        <v>0.91955914431135433</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4470,14 +4470,14 @@
       </c>
       <c r="T26" s="6">
         <f t="shared" si="6"/>
-        <v>8450</v>
+        <v>8453</v>
       </c>
       <c r="U26" s="5">
-        <v>11302</v>
+        <v>11305</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="7"/>
-        <v>0.68600910470409715</v>
+        <v>0.6861911987860394</v>
       </c>
       <c r="W26" s="5">
         <v>16675</v>
@@ -4487,14 +4487,14 @@
       </c>
       <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>7990</v>
+        <v>7994</v>
       </c>
       <c r="Z26" s="5">
-        <v>11454</v>
+        <v>11458</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="9"/>
-        <v>0.68689655172413788</v>
+        <v>0.68713643178410799</v>
       </c>
       <c r="AB26" s="6">
         <v>25656</v>
@@ -4504,14 +4504,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>12771</v>
+        <v>12779</v>
       </c>
       <c r="AE26" s="5">
-        <v>19361</v>
+        <v>19369</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.75463829123791704</v>
+        <v>0.75495010913626437</v>
       </c>
       <c r="AG26" s="5">
         <v>15844</v>
@@ -4521,14 +4521,14 @@
       </c>
       <c r="AI26" s="6">
         <f t="shared" si="12"/>
-        <v>7387</v>
+        <v>7394</v>
       </c>
       <c r="AJ26" s="5">
-        <v>11197</v>
+        <v>11204</v>
       </c>
       <c r="AK26" s="7">
         <f t="shared" si="13"/>
-        <v>0.70670285281494571</v>
+        <v>0.70714466043928303</v>
       </c>
       <c r="AL26" s="5">
         <v>16081</v>
@@ -4538,14 +4538,14 @@
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="14"/>
-        <v>3586</v>
+        <v>3593</v>
       </c>
       <c r="AO26" s="5">
-        <v>11426</v>
+        <v>11433</v>
       </c>
       <c r="AP26" s="7">
         <f t="shared" si="15"/>
-        <v>0.71052795224177601</v>
+        <v>0.71096324855419435</v>
       </c>
       <c r="AQ26" s="6">
         <v>26317</v>
@@ -4555,14 +4555,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>13381</v>
+        <v>13389</v>
       </c>
       <c r="AT26" s="5">
-        <v>20107</v>
+        <v>20115</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.76403085458068931</v>
+        <v>0.76433484059733248</v>
       </c>
       <c r="AV26" s="5">
         <v>15987</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="AX26" s="6">
         <f t="shared" si="18"/>
-        <v>7195</v>
+        <v>7200</v>
       </c>
       <c r="AY26" s="5">
-        <v>11383</v>
+        <v>11388</v>
       </c>
       <c r="AZ26" s="7">
         <f t="shared" si="19"/>
-        <v>0.71201601301057105</v>
+        <v>0.71232876712328763</v>
       </c>
       <c r="BA26" s="5">
         <v>16133</v>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="BC26" s="6">
         <f t="shared" si="20"/>
-        <v>7247</v>
+        <v>7252</v>
       </c>
       <c r="BD26" s="5">
-        <v>11569</v>
+        <v>11574</v>
       </c>
       <c r="BE26" s="7">
         <f t="shared" si="21"/>
-        <v>0.71710159300812004</v>
+        <v>0.71741151676687531</v>
       </c>
       <c r="BF26" s="5">
         <v>26642</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>13815</v>
+        <v>13821</v>
       </c>
       <c r="BI26" s="5">
-        <v>20669</v>
+        <v>20675</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.77580511973575561</v>
+        <v>0.7760303280534494</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4682,14 +4682,14 @@
       </c>
       <c r="T27" s="6">
         <f t="shared" si="6"/>
-        <v>70966</v>
+        <v>70968</v>
       </c>
       <c r="U27" s="5">
-        <v>99664</v>
+        <v>99666</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="7"/>
-        <v>0.88130377496971357</v>
+        <v>0.88132146046848892</v>
       </c>
       <c r="W27" s="5">
         <v>116164</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="Y27" s="6">
         <f t="shared" si="8"/>
-        <v>68640</v>
+        <v>68644</v>
       </c>
       <c r="Z27" s="5">
-        <v>102905</v>
+        <v>102909</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="9"/>
-        <v>0.88585964670638062</v>
+        <v>0.88589408078234222</v>
       </c>
       <c r="AB27" s="6">
         <v>165468</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AD27" s="6">
         <f t="shared" si="10"/>
-        <v>87058</v>
+        <v>87063</v>
       </c>
       <c r="AE27" s="5">
-        <v>147899</v>
+        <v>147904</v>
       </c>
       <c r="AF27" s="7">
         <f t="shared" si="11"/>
-        <v>0.89382237048855373</v>
+        <v>0.89385258781154064</v>
       </c>
       <c r="AG27" s="5">
         <v>116084</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AI27" s="6">
         <f t="shared" si="12"/>
-        <v>63657</v>
+        <v>63661</v>
       </c>
       <c r="AJ27" s="5">
-        <v>102272</v>
+        <v>102276</v>
       </c>
       <c r="AK27" s="7">
         <f t="shared" si="13"/>
-        <v>0.88101719444540161</v>
+        <v>0.8810516522518177</v>
       </c>
       <c r="AL27" s="5">
         <v>117992</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AN27" s="6">
         <f t="shared" si="14"/>
-        <v>33234</v>
+        <v>33239</v>
       </c>
       <c r="AO27" s="5">
-        <v>104350</v>
+        <v>104355</v>
       </c>
       <c r="AP27" s="7">
         <f t="shared" si="15"/>
-        <v>0.88438199199945755</v>
+        <v>0.884424367753746</v>
       </c>
       <c r="AQ27" s="6">
         <v>170879</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>94820</v>
+        <v>94828</v>
       </c>
       <c r="AT27" s="5">
-        <v>153099</v>
+        <v>153107</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.89594976562362838</v>
+        <v>0.89599658237700364</v>
       </c>
       <c r="AV27" s="5">
         <v>116485</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AX27" s="6">
         <f t="shared" si="18"/>
-        <v>62246</v>
+        <v>62253</v>
       </c>
       <c r="AY27" s="5">
-        <v>105083</v>
+        <v>105090</v>
       </c>
       <c r="AZ27" s="7">
         <f t="shared" si="19"/>
-        <v>0.90211615229428677</v>
+        <v>0.90217624586856682</v>
       </c>
       <c r="BA27" s="5">
         <v>117017</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BC27" s="6">
         <f t="shared" si="20"/>
-        <v>62163</v>
+        <v>62170</v>
       </c>
       <c r="BD27" s="5">
-        <v>106745</v>
+        <v>106752</v>
       </c>
       <c r="BE27" s="7">
         <f t="shared" si="21"/>
-        <v>0.91221788287171945</v>
+        <v>0.91227770323970026</v>
       </c>
       <c r="BF27" s="5">
         <v>172738</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>103542</v>
+        <v>103550</v>
       </c>
       <c r="BI27" s="5">
-        <v>156646</v>
+        <v>156654</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.90684157510217789</v>
+        <v>0.9068878880153759</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="T28" s="6">
         <f t="shared" si="6"/>
-        <v>170718</v>
+        <v>170719</v>
       </c>
       <c r="U28" s="5">
-        <v>318468</v>
+        <v>318469</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="7"/>
-        <v>0.83851942348300934</v>
+        <v>0.83852205646159272</v>
       </c>
       <c r="W28" s="5">
         <v>378910</v>
@@ -4911,14 +4911,14 @@
       </c>
       <c r="Y28" s="6">
         <f t="shared" si="8"/>
-        <v>163231</v>
+        <v>163232</v>
       </c>
       <c r="Z28" s="5">
-        <v>322476</v>
+        <v>322477</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="9"/>
-        <v>0.85106225752817288</v>
+        <v>0.85106489667731122</v>
       </c>
       <c r="AB28" s="6">
         <v>628364</v>
@@ -4928,14 +4928,14 @@
       </c>
       <c r="AD28" s="6">
         <f t="shared" si="10"/>
-        <v>254361</v>
+        <v>254362</v>
       </c>
       <c r="AE28" s="5">
-        <v>559993</v>
+        <v>559994</v>
       </c>
       <c r="AF28" s="7">
         <f t="shared" si="11"/>
-        <v>0.8911920479212686</v>
+        <v>0.89119363935553275</v>
       </c>
       <c r="AG28" s="5">
         <v>375124</v>
@@ -4945,14 +4945,14 @@
       </c>
       <c r="AI28" s="6">
         <f t="shared" si="12"/>
-        <v>152978</v>
+        <v>152979</v>
       </c>
       <c r="AJ28" s="5">
-        <v>323065</v>
+        <v>323066</v>
       </c>
       <c r="AK28" s="7">
         <f t="shared" si="13"/>
-        <v>0.86122188929527299</v>
+        <v>0.86122455508045337</v>
       </c>
       <c r="AL28" s="5">
         <v>368781</v>
@@ -4962,14 +4962,14 @@
       </c>
       <c r="AN28" s="6">
         <f t="shared" si="14"/>
-        <v>60410</v>
+        <v>60411</v>
       </c>
       <c r="AO28" s="5">
-        <v>328469</v>
+        <v>328470</v>
       </c>
       <c r="AP28" s="7">
         <f t="shared" si="15"/>
-        <v>0.89068851160987139</v>
+        <v>0.89069122324631689</v>
       </c>
       <c r="AQ28" s="6">
         <v>617418</v>
@@ -4979,14 +4979,14 @@
       </c>
       <c r="AS28" s="6">
         <f t="shared" si="16"/>
-        <v>275504</v>
+        <v>275506</v>
       </c>
       <c r="AT28" s="5">
-        <v>571903</v>
+        <v>571905</v>
       </c>
       <c r="AU28" s="7">
         <f t="shared" si="17"/>
-        <v>0.9262817086641465</v>
+        <v>0.92628494796070082</v>
       </c>
       <c r="AV28" s="5">
         <v>357852</v>
@@ -4996,14 +4996,14 @@
       </c>
       <c r="AX28" s="6">
         <f t="shared" si="18"/>
-        <v>144542</v>
+        <v>144543</v>
       </c>
       <c r="AY28" s="5">
-        <v>331105</v>
+        <v>331106</v>
       </c>
       <c r="AZ28" s="7">
         <f t="shared" si="19"/>
-        <v>0.92525681007790928</v>
+        <v>0.92525960452924672</v>
       </c>
       <c r="BA28" s="5">
         <v>359943</v>
@@ -5013,14 +5013,14 @@
       </c>
       <c r="BC28" s="6">
         <f t="shared" si="20"/>
-        <v>140365</v>
+        <v>140367</v>
       </c>
       <c r="BD28" s="5">
-        <v>335597</v>
+        <v>335599</v>
       </c>
       <c r="BE28" s="7">
         <f t="shared" si="21"/>
-        <v>0.93236151279508139</v>
+        <v>0.93236706923040591</v>
       </c>
       <c r="BF28" s="5">
         <v>622234</v>
@@ -5030,14 +5030,14 @@
       </c>
       <c r="BH28" s="6">
         <f t="shared" si="22"/>
-        <v>281150</v>
+        <v>281152</v>
       </c>
       <c r="BI28" s="5">
-        <v>582340</v>
+        <v>582342</v>
       </c>
       <c r="BJ28" s="7">
         <f t="shared" si="23"/>
-        <v>0.93588585644628874</v>
+        <v>0.93588907067116234</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5106,14 +5106,14 @@
       </c>
       <c r="T29" s="6">
         <f t="shared" si="6"/>
-        <v>61573</v>
+        <v>61574</v>
       </c>
       <c r="U29" s="5">
-        <v>103722</v>
+        <v>103723</v>
       </c>
       <c r="V29" s="7">
         <f t="shared" si="7"/>
-        <v>0.92743074804628123</v>
+        <v>0.92743968955095768</v>
       </c>
       <c r="W29" s="5">
         <v>113722</v>
@@ -5123,14 +5123,14 @@
       </c>
       <c r="Y29" s="6">
         <f t="shared" si="8"/>
-        <v>58675</v>
+        <v>58676</v>
       </c>
       <c r="Z29" s="5">
-        <v>105048</v>
+        <v>105049</v>
       </c>
       <c r="AA29" s="7">
         <f t="shared" si="9"/>
-        <v>0.92372627987548583</v>
+        <v>0.92373507324879967</v>
       </c>
       <c r="AB29" s="6">
         <v>160157</v>
@@ -5140,14 +5140,14 @@
       </c>
       <c r="AD29" s="6">
         <f t="shared" si="10"/>
-        <v>76485</v>
+        <v>76487</v>
       </c>
       <c r="AE29" s="5">
-        <v>149212</v>
+        <v>149214</v>
       </c>
       <c r="AF29" s="7">
         <f t="shared" si="11"/>
-        <v>0.93166080783231453</v>
+        <v>0.93167329557871337</v>
       </c>
       <c r="AG29" s="5">
         <v>115309</v>
@@ -5157,14 +5157,14 @@
       </c>
       <c r="AI29" s="6">
         <f t="shared" si="12"/>
-        <v>61729</v>
+        <v>61730</v>
       </c>
       <c r="AJ29" s="5">
-        <v>106348</v>
+        <v>106349</v>
       </c>
       <c r="AK29" s="7">
         <f t="shared" si="13"/>
-        <v>0.92228707212793448</v>
+        <v>0.92229574447788121</v>
       </c>
       <c r="AL29" s="5">
         <v>116530</v>
@@ -5174,14 +5174,14 @@
       </c>
       <c r="AN29" s="6">
         <f t="shared" si="14"/>
-        <v>22821</v>
+        <v>22823</v>
       </c>
       <c r="AO29" s="5">
-        <v>107885</v>
+        <v>107887</v>
       </c>
       <c r="AP29" s="7">
         <f t="shared" si="15"/>
-        <v>0.92581309534025569</v>
+        <v>0.92583025830258303</v>
       </c>
       <c r="AQ29" s="6">
         <v>164389</v>
@@ -5191,14 +5191,14 @@
       </c>
       <c r="AS29" s="6">
         <f t="shared" si="16"/>
-        <v>81643</v>
+        <v>81646</v>
       </c>
       <c r="AT29" s="5">
-        <v>153099</v>
+        <v>153102</v>
       </c>
       <c r="AU29" s="7">
         <f t="shared" si="17"/>
-        <v>0.93132143878240026</v>
+        <v>0.93133968817864943</v>
       </c>
       <c r="AV29" s="5">
         <v>118862</v>
@@ -5208,14 +5208,14 @@
       </c>
       <c r="AX29" s="6">
         <f t="shared" si="18"/>
-        <v>54653</v>
+        <v>54655</v>
       </c>
       <c r="AY29" s="5">
-        <v>109746</v>
+        <v>109748</v>
       </c>
       <c r="AZ29" s="7">
         <f t="shared" si="19"/>
-        <v>0.9233060187444263</v>
+        <v>0.9233228449798927</v>
       </c>
       <c r="BA29" s="5">
         <v>119046</v>
@@ -5225,14 +5225,14 @@
       </c>
       <c r="BC29" s="6">
         <f t="shared" si="20"/>
-        <v>53037</v>
+        <v>53039</v>
       </c>
       <c r="BD29" s="5">
-        <v>111244</v>
+        <v>111246</v>
       </c>
       <c r="BE29" s="7">
         <f t="shared" si="21"/>
-        <v>0.9344623086873981</v>
+        <v>0.93447910891588126</v>
       </c>
       <c r="BF29" s="5">
         <v>167253</v>
@@ -5242,14 +5242,14 @@
       </c>
       <c r="BH29" s="6">
         <f t="shared" si="22"/>
-        <v>89127</v>
+        <v>89130</v>
       </c>
       <c r="BI29" s="5">
-        <v>156296</v>
+        <v>156299</v>
       </c>
       <c r="BJ29" s="7">
         <f t="shared" si="23"/>
-        <v>0.93448846956407361</v>
+        <v>0.9345064064620664</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="AI30" s="6">
         <f t="shared" si="12"/>
-        <v>82964</v>
+        <v>82965</v>
       </c>
       <c r="AJ30" s="5">
-        <v>137368</v>
+        <v>137369</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="13"/>
-        <v>0.89678674483280885</v>
+        <v>0.89679327318544444</v>
       </c>
       <c r="AL30" s="5">
         <v>156106</v>
@@ -5386,14 +5386,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>37359</v>
+        <v>37360</v>
       </c>
       <c r="AO30" s="5">
-        <v>141051</v>
+        <v>141052</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.90355912008507044</v>
+        <v>0.90356552598875128</v>
       </c>
       <c r="AQ30" s="6">
         <v>266513</v>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>155906</v>
+        <v>155907</v>
       </c>
       <c r="BI30" s="5">
-        <v>247615</v>
+        <v>247616</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.91509632690168485</v>
+        <v>0.9151000225434146</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5530,14 +5530,14 @@
       </c>
       <c r="T31" s="6">
         <f t="shared" si="6"/>
-        <v>42984</v>
+        <v>42985</v>
       </c>
       <c r="U31" s="5">
-        <v>67153</v>
+        <v>67154</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="7"/>
-        <v>0.92226662821199512</v>
+        <v>0.92228036202326502</v>
       </c>
       <c r="W31" s="5">
         <v>74776</v>
@@ -5547,14 +5547,14 @@
       </c>
       <c r="Y31" s="6">
         <f t="shared" si="8"/>
-        <v>42004</v>
+        <v>42007</v>
       </c>
       <c r="Z31" s="5">
-        <v>68808</v>
+        <v>68811</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="9"/>
-        <v>0.92018829570985339</v>
+        <v>0.92022841553439605</v>
       </c>
       <c r="AB31" s="6">
         <v>124489</v>
@@ -5564,14 +5564,14 @@
       </c>
       <c r="AD31" s="6">
         <f t="shared" si="10"/>
-        <v>65124</v>
+        <v>65129</v>
       </c>
       <c r="AE31" s="5">
-        <v>116350</v>
+        <v>116355</v>
       </c>
       <c r="AF31" s="7">
         <f t="shared" si="11"/>
-        <v>0.93462072954236919</v>
+        <v>0.93466089373358285</v>
       </c>
       <c r="AG31" s="5">
         <v>73552</v>
@@ -5581,14 +5581,14 @@
       </c>
       <c r="AI31" s="6">
         <f t="shared" si="12"/>
-        <v>38803</v>
+        <v>38804</v>
       </c>
       <c r="AJ31" s="5">
-        <v>67169</v>
+        <v>67170</v>
       </c>
       <c r="AK31" s="7">
         <f t="shared" si="13"/>
-        <v>0.9132178594735697</v>
+        <v>0.91323145529693284</v>
       </c>
       <c r="AL31" s="5">
         <v>74464</v>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>67773</v>
+        <v>67776</v>
       </c>
       <c r="AT31" s="5">
-        <v>119015</v>
+        <v>119018</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.93974543214945594</v>
+        <v>0.9397691202248788</v>
       </c>
       <c r="AV31" s="5">
         <v>72827</v>
@@ -5666,14 +5666,14 @@
       </c>
       <c r="BH31" s="6">
         <f t="shared" si="22"/>
-        <v>72577</v>
+        <v>72580</v>
       </c>
       <c r="BI31" s="5">
-        <v>121955</v>
+        <v>121958</v>
       </c>
       <c r="BJ31" s="7">
         <f t="shared" si="23"/>
-        <v>0.94133765582185169</v>
+        <v>0.94136081201034305</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5742,14 +5742,14 @@
       </c>
       <c r="T32" s="6">
         <f t="shared" si="6"/>
-        <v>109774</v>
+        <v>109776</v>
       </c>
       <c r="U32" s="5">
-        <v>173281</v>
+        <v>173283</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="7"/>
-        <v>0.94056374877192217</v>
+        <v>0.94057460470821952</v>
       </c>
       <c r="W32" s="5">
         <v>187639</v>
@@ -5759,14 +5759,14 @@
       </c>
       <c r="Y32" s="6">
         <f t="shared" si="8"/>
-        <v>107226</v>
+        <v>107228</v>
       </c>
       <c r="Z32" s="5">
-        <v>177608</v>
+        <v>177610</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="9"/>
-        <v>0.94654096429846679</v>
+        <v>0.94655162306343565</v>
       </c>
       <c r="AB32" s="6">
         <v>392348</v>
@@ -5776,14 +5776,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>213236</v>
+        <v>213238</v>
       </c>
       <c r="AE32" s="5">
-        <v>373033</v>
+        <v>373035</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.95077074433920905</v>
+        <v>0.95077584185468</v>
       </c>
       <c r="AG32" s="5">
         <v>183147</v>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="AI32" s="6">
         <f t="shared" si="12"/>
-        <v>99027</v>
+        <v>99029</v>
       </c>
       <c r="AJ32" s="5">
-        <v>174271</v>
+        <v>174273</v>
       </c>
       <c r="AK32" s="7">
         <f t="shared" si="13"/>
-        <v>0.95153619769911602</v>
+        <v>0.95154711788890889</v>
       </c>
       <c r="AL32" s="5">
         <v>187303</v>
@@ -5810,14 +5810,14 @@
       </c>
       <c r="AN32" s="6">
         <f t="shared" si="14"/>
-        <v>44652</v>
+        <v>44654</v>
       </c>
       <c r="AO32" s="5">
-        <v>178175</v>
+        <v>178177</v>
       </c>
       <c r="AP32" s="7">
         <f t="shared" si="15"/>
-        <v>0.95126613028088181</v>
+        <v>0.95127680816644689</v>
       </c>
       <c r="AQ32" s="6">
         <v>402574</v>
@@ -5827,14 +5827,14 @@
       </c>
       <c r="AS32" s="6">
         <f t="shared" si="16"/>
-        <v>213496</v>
+        <v>213499</v>
       </c>
       <c r="AT32" s="5">
-        <v>382383</v>
+        <v>382386</v>
       </c>
       <c r="AU32" s="7">
         <f t="shared" si="17"/>
-        <v>0.94984524584300034</v>
+        <v>0.94985269788908377</v>
       </c>
       <c r="AV32" s="5">
         <v>187080</v>
@@ -5844,14 +5844,14 @@
       </c>
       <c r="AX32" s="6">
         <f t="shared" si="18"/>
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="AY32" s="5">
-        <v>178095</v>
+        <v>178098</v>
       </c>
       <c r="AZ32" s="7">
         <f t="shared" si="19"/>
-        <v>0.95197241821680567</v>
+        <v>0.95198845413726751</v>
       </c>
       <c r="BA32" s="5">
         <v>189893</v>
@@ -5861,14 +5861,14 @@
       </c>
       <c r="BC32" s="6">
         <f t="shared" si="20"/>
-        <v>79049</v>
+        <v>79052</v>
       </c>
       <c r="BD32" s="5">
-        <v>182599</v>
+        <v>182602</v>
       </c>
       <c r="BE32" s="7">
         <f t="shared" si="21"/>
-        <v>0.96158889479864973</v>
+        <v>0.96160469316931119</v>
       </c>
       <c r="BF32" s="5">
         <v>410654</v>
@@ -5878,14 +5878,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>227771</v>
+        <v>227775</v>
       </c>
       <c r="BI32" s="5">
-        <v>388852</v>
+        <v>388856</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.94690907674100333</v>
+        <v>0.94691881730118299</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="T33" s="6">
         <f t="shared" si="6"/>
-        <v>150541</v>
+        <v>150543</v>
       </c>
       <c r="U33" s="5">
-        <v>549206</v>
+        <v>549208</v>
       </c>
       <c r="V33" s="7">
         <f t="shared" si="7"/>
-        <v>0.97416158631222138</v>
+        <v>0.9741651338393289</v>
       </c>
       <c r="W33" s="5">
         <v>571583</v>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="Y33" s="6">
         <f t="shared" si="8"/>
-        <v>139904</v>
+        <v>139905</v>
       </c>
       <c r="Z33" s="5">
-        <v>554807</v>
+        <v>554808</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="9"/>
-        <v>0.97064993185591597</v>
+        <v>0.9706516813831062</v>
       </c>
       <c r="AB33" s="6">
         <v>961057</v>
@@ -5988,14 +5988,14 @@
       </c>
       <c r="AD33" s="6">
         <f t="shared" si="10"/>
-        <v>220240</v>
+        <v>220241</v>
       </c>
       <c r="AE33" s="5">
-        <v>941305</v>
+        <v>941306</v>
       </c>
       <c r="AF33" s="7">
         <f t="shared" si="11"/>
-        <v>0.97944762901680127</v>
+        <v>0.97944866953781096</v>
       </c>
       <c r="AG33" s="5">
         <v>565645</v>
@@ -6005,14 +6005,14 @@
       </c>
       <c r="AI33" s="6">
         <f t="shared" si="12"/>
-        <v>154558</v>
+        <v>154559</v>
       </c>
       <c r="AJ33" s="5">
-        <v>550823</v>
+        <v>550824</v>
       </c>
       <c r="AK33" s="7">
         <f t="shared" si="13"/>
-        <v>0.9737962856561978</v>
+        <v>0.97379805354948779</v>
       </c>
       <c r="AL33" s="5">
         <v>569536</v>
@@ -6022,14 +6022,14 @@
       </c>
       <c r="AN33" s="6">
         <f t="shared" si="14"/>
-        <v>52853</v>
+        <v>52854</v>
       </c>
       <c r="AO33" s="5">
-        <v>556516</v>
+        <v>556517</v>
       </c>
       <c r="AP33" s="7">
         <f t="shared" si="15"/>
-        <v>0.97713928531295646</v>
+        <v>0.97714104112821665</v>
       </c>
       <c r="AQ33" s="6">
         <v>971221</v>
@@ -6056,14 +6056,14 @@
       </c>
       <c r="AX33" s="6">
         <f t="shared" si="18"/>
-        <v>101113</v>
+        <v>101114</v>
       </c>
       <c r="AY33" s="5">
-        <v>560632</v>
+        <v>560633</v>
       </c>
       <c r="AZ33" s="7">
         <f t="shared" si="19"/>
-        <v>0.9817151542532141</v>
+        <v>0.9817169053397633</v>
       </c>
       <c r="BA33" s="5">
         <v>575700</v>
@@ -6073,14 +6073,14 @@
       </c>
       <c r="BC33" s="6">
         <f t="shared" si="20"/>
-        <v>95013</v>
+        <v>95014</v>
       </c>
       <c r="BD33" s="5">
-        <v>570885</v>
+        <v>570886</v>
       </c>
       <c r="BE33" s="7">
         <f t="shared" si="21"/>
-        <v>0.99163626889004686</v>
+        <v>0.99163800590585371</v>
       </c>
       <c r="BF33" s="5">
         <v>986775</v>
@@ -6090,14 +6090,14 @@
       </c>
       <c r="BH33" s="6">
         <f t="shared" si="22"/>
-        <v>221382</v>
+        <v>221385</v>
       </c>
       <c r="BI33" s="5">
-        <v>972682</v>
+        <v>972685</v>
       </c>
       <c r="BJ33" s="7">
         <f t="shared" si="23"/>
-        <v>0.98571812216564059</v>
+        <v>0.98572116237237462</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6566,14 +6566,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>349417</v>
+        <v>349427</v>
       </c>
       <c r="U36" s="5">
-        <v>717603</v>
+        <v>717613</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.94670580474934041</v>
+        <v>0.94671899736147758</v>
       </c>
       <c r="W36" s="5">
         <v>766789</v>
@@ -6583,14 +6583,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>352542</v>
+        <v>352552</v>
       </c>
       <c r="Z36" s="5">
-        <v>731802</v>
+        <v>731812</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.95437206324034385</v>
+        <v>0.95438510463765125</v>
       </c>
       <c r="AB36" s="6">
         <v>1410553</v>
@@ -6600,14 +6600,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>580371</v>
+        <v>580380</v>
       </c>
       <c r="AE36" s="5">
-        <v>1353320</v>
+        <v>1353329</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.95942513326333712</v>
+        <v>0.95943151373964675</v>
       </c>
       <c r="AG36" s="5">
         <v>767229</v>
@@ -6617,14 +6617,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>321704</v>
+        <v>321713</v>
       </c>
       <c r="AJ36" s="5">
-        <v>729741</v>
+        <v>729750</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.95113844758214305</v>
+        <v>0.95115017810849167</v>
       </c>
       <c r="AL36" s="5">
         <v>779513</v>
@@ -6634,14 +6634,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>159026</v>
+        <v>159033</v>
       </c>
       <c r="AO36" s="5">
-        <v>741658</v>
+        <v>741665</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.95143762836540247</v>
+        <v>0.95144660833109906</v>
       </c>
       <c r="AQ36" s="6">
         <v>1443943</v>
@@ -6651,14 +6651,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>553787</v>
+        <v>553796</v>
       </c>
       <c r="AT36" s="5">
-        <v>1380654</v>
+        <v>1380663</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.95616932247325548</v>
+        <v>0.95617555540627297</v>
       </c>
       <c r="AV36" s="5">
         <v>783108</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>259345</v>
+        <v>259350</v>
       </c>
       <c r="AY36" s="5">
-        <v>745643</v>
+        <v>745648</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.95215857838254747</v>
+        <v>0.95216496319792421</v>
       </c>
       <c r="BA36" s="5">
         <v>793830</v>
@@ -6685,14 +6685,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>252879</v>
+        <v>252883</v>
       </c>
       <c r="BD36" s="5">
-        <v>759225</v>
+        <v>759229</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.9564075431767507</v>
+        <v>0.95641258203897561</v>
       </c>
       <c r="BF36" s="5">
         <v>1468416</v>
@@ -6702,14 +6702,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="24"/>
-        <v>554475</v>
+        <v>554484</v>
       </c>
       <c r="BI36" s="5">
-        <v>1403646</v>
+        <v>1403655</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="25"/>
-        <v>0.95589124607740583</v>
+        <v>0.95589737513075312</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6778,14 +6778,14 @@
       </c>
       <c r="T37" s="6">
         <f t="shared" si="6"/>
-        <v>294918</v>
+        <v>294927</v>
       </c>
       <c r="U37" s="5">
-        <v>556562</v>
+        <v>556571</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="7"/>
-        <v>0.92512861429010729</v>
+        <v>0.92514357427215532</v>
       </c>
       <c r="W37" s="5">
         <v>609453</v>
@@ -6795,14 +6795,14 @@
       </c>
       <c r="Y37" s="6">
         <f t="shared" si="8"/>
-        <v>298803</v>
+        <v>298811</v>
       </c>
       <c r="Z37" s="5">
-        <v>564840</v>
+        <v>564848</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="9"/>
-        <v>0.92679829289543247</v>
+        <v>0.92681141942036549</v>
       </c>
       <c r="AB37" s="6">
         <v>790568</v>
@@ -6812,14 +6812,14 @@
       </c>
       <c r="AD37" s="6">
         <f t="shared" si="10"/>
-        <v>342031</v>
+        <v>342042</v>
       </c>
       <c r="AE37" s="5">
-        <v>735806</v>
+        <v>735817</v>
       </c>
       <c r="AF37" s="7">
         <f t="shared" si="11"/>
-        <v>0.93073081632446542</v>
+        <v>0.93074473037107497</v>
       </c>
       <c r="AG37" s="5">
         <v>617773</v>
@@ -6829,14 +6829,14 @@
       </c>
       <c r="AI37" s="6">
         <f t="shared" si="12"/>
-        <v>268101</v>
+        <v>268110</v>
       </c>
       <c r="AJ37" s="5">
-        <v>572937</v>
+        <v>572946</v>
       </c>
       <c r="AK37" s="7">
         <f t="shared" si="13"/>
-        <v>0.92742317971164168</v>
+        <v>0.92743774816963509</v>
       </c>
       <c r="AL37" s="5">
         <v>624724</v>
@@ -6846,14 +6846,14 @@
       </c>
       <c r="AN37" s="6">
         <f t="shared" si="14"/>
-        <v>101173</v>
+        <v>101180</v>
       </c>
       <c r="AO37" s="5">
-        <v>581027</v>
+        <v>581034</v>
       </c>
       <c r="AP37" s="7">
         <f t="shared" si="15"/>
-        <v>0.93005391180745423</v>
+        <v>0.93006511675555925</v>
       </c>
       <c r="AQ37" s="6">
         <v>810789</v>
@@ -6863,14 +6863,14 @@
       </c>
       <c r="AS37" s="6">
         <f t="shared" si="16"/>
-        <v>350643</v>
+        <v>350652</v>
       </c>
       <c r="AT37" s="5">
-        <v>756836</v>
+        <v>756845</v>
       </c>
       <c r="AU37" s="7">
         <f t="shared" si="17"/>
-        <v>0.93345617663781821</v>
+        <v>0.93346727693641629</v>
       </c>
       <c r="AV37" s="5">
         <v>633338</v>
@@ -6880,14 +6880,14 @@
       </c>
       <c r="AX37" s="6">
         <f t="shared" si="18"/>
-        <v>242773</v>
+        <v>242780</v>
       </c>
       <c r="AY37" s="5">
-        <v>591838</v>
+        <v>591845</v>
       </c>
       <c r="AZ37" s="7">
         <f t="shared" si="19"/>
-        <v>0.93447416703245345</v>
+        <v>0.93448521958259256</v>
       </c>
       <c r="BA37" s="5">
         <v>640933</v>
@@ -6897,14 +6897,14 @@
       </c>
       <c r="BC37" s="6">
         <f t="shared" si="20"/>
-        <v>236707</v>
+        <v>236713</v>
       </c>
       <c r="BD37" s="5">
-        <v>600819</v>
+        <v>600825</v>
       </c>
       <c r="BE37" s="7">
         <f t="shared" si="21"/>
-        <v>0.93741311494337165</v>
+        <v>0.93742247629627429</v>
       </c>
       <c r="BF37" s="5">
         <v>830528</v>
@@ -6914,14 +6914,14 @@
       </c>
       <c r="BH37" s="6">
         <f t="shared" si="24"/>
-        <v>361794</v>
+        <v>361805</v>
       </c>
       <c r="BI37" s="5">
-        <v>776611</v>
+        <v>776622</v>
       </c>
       <c r="BJ37" s="7">
         <f t="shared" si="25"/>
-        <v>0.93508105686984666</v>
+        <v>0.93509430145642292</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7414,14 +7414,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>121905</v>
+        <v>121906</v>
       </c>
       <c r="U40" s="5">
-        <v>242363</v>
+        <v>242364</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.94177145344047752</v>
+        <v>0.9417753392293704</v>
       </c>
       <c r="W40" s="5">
         <v>259512</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>111095</v>
+        <v>111097</v>
       </c>
       <c r="Z40" s="5">
-        <v>244318</v>
+        <v>244320</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.94145164770800582</v>
+        <v>0.9414593544807176</v>
       </c>
       <c r="AB40" s="6">
         <v>322067</v>
@@ -7448,14 +7448,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>125324</v>
+        <v>125326</v>
       </c>
       <c r="AE40" s="5">
-        <v>305020</v>
+        <v>305022</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.94707001959219661</v>
+        <v>0.94707622948020131</v>
       </c>
       <c r="AG40" s="5">
         <v>262041</v>
@@ -7465,14 +7465,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="AJ40" s="5">
-        <v>247112</v>
+        <v>247114</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.94302799943520288</v>
+        <v>0.94303563182860695</v>
       </c>
       <c r="AL40" s="5">
         <v>264607</v>
@@ -7482,14 +7482,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>39746</v>
+        <v>39748</v>
       </c>
       <c r="AO40" s="5">
-        <v>250047</v>
+        <v>250049</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.9449750006613582</v>
+        <v>0.94498255904038819</v>
       </c>
       <c r="AQ40" s="6">
         <v>328683</v>
@@ -7499,14 +7499,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>125224</v>
+        <v>125228</v>
       </c>
       <c r="AT40" s="5">
-        <v>312605</v>
+        <v>312609</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.95108356684099882</v>
+        <v>0.95109573662160807</v>
       </c>
       <c r="AV40" s="5">
         <v>267796</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>91426</v>
+        <v>91430</v>
       </c>
       <c r="AY40" s="5">
-        <v>253326</v>
+        <v>253330</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.9459663325815173</v>
+        <v>0.94598126932441107</v>
       </c>
       <c r="BA40" s="5">
         <v>270158</v>
@@ -7533,14 +7533,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>92574</v>
+        <v>92578</v>
       </c>
       <c r="BD40" s="5">
-        <v>256025</v>
+        <v>256029</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.94768616883453383</v>
+        <v>0.94770097498500883</v>
       </c>
       <c r="BF40" s="5">
         <v>335514</v>
@@ -7550,14 +7550,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="24"/>
-        <v>137579</v>
+        <v>137584</v>
       </c>
       <c r="BI40" s="5">
-        <v>318085</v>
+        <v>318090</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="25"/>
-        <v>0.94805283833163445</v>
+        <v>0.94806774083942846</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7626,14 +7626,14 @@
       </c>
       <c r="T41" s="6">
         <f t="shared" si="6"/>
-        <v>371908</v>
+        <v>371929</v>
       </c>
       <c r="U41" s="5">
-        <v>778628</v>
+        <v>778649</v>
       </c>
       <c r="V41" s="7">
         <f t="shared" si="7"/>
-        <v>0.94703669422372172</v>
+        <v>0.94706223629333486</v>
       </c>
       <c r="W41" s="5">
         <v>833879</v>
@@ -7643,14 +7643,14 @@
       </c>
       <c r="Y41" s="6">
         <f t="shared" si="8"/>
-        <v>376226</v>
+        <v>376249</v>
       </c>
       <c r="Z41" s="5">
-        <v>786072</v>
+        <v>786095</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="9"/>
-        <v>0.94266914024696624</v>
+        <v>0.9426967221863124</v>
       </c>
       <c r="AB41" s="6">
         <v>956956</v>
@@ -7660,14 +7660,14 @@
       </c>
       <c r="AD41" s="6">
         <f t="shared" si="10"/>
-        <v>367869</v>
+        <v>367892</v>
       </c>
       <c r="AE41" s="5">
-        <v>899990</v>
+        <v>900013</v>
       </c>
       <c r="AF41" s="7">
         <f t="shared" si="11"/>
-        <v>0.94047166222898437</v>
+        <v>0.94049569677184741</v>
       </c>
       <c r="AG41" s="5">
         <v>851169</v>
@@ -7677,14 +7677,14 @@
       </c>
       <c r="AI41" s="6">
         <f t="shared" si="12"/>
-        <v>370398</v>
+        <v>370420</v>
       </c>
       <c r="AJ41" s="5">
-        <v>798531</v>
+        <v>798553</v>
       </c>
       <c r="AK41" s="7">
         <f t="shared" si="13"/>
-        <v>0.93815799212612305</v>
+        <v>0.938183838932104</v>
       </c>
       <c r="AL41" s="5">
         <v>859964</v>
@@ -7694,14 +7694,14 @@
       </c>
       <c r="AN41" s="6">
         <f t="shared" si="14"/>
-        <v>118001</v>
+        <v>118021</v>
       </c>
       <c r="AO41" s="5">
-        <v>807024</v>
+        <v>807044</v>
       </c>
       <c r="AP41" s="7">
         <f t="shared" si="15"/>
-        <v>0.93843928350489092</v>
+        <v>0.9384625402923843</v>
       </c>
       <c r="AQ41" s="6">
         <v>982238</v>
@@ -7711,14 +7711,14 @@
       </c>
       <c r="AS41" s="6">
         <f t="shared" si="16"/>
-        <v>370278</v>
+        <v>370302</v>
       </c>
       <c r="AT41" s="5">
-        <v>921153</v>
+        <v>921177</v>
       </c>
       <c r="AU41" s="7">
         <f t="shared" si="17"/>
-        <v>0.93781038811367512</v>
+        <v>0.93783482211032354</v>
       </c>
       <c r="AV41" s="5">
         <v>867973</v>
@@ -7728,14 +7728,14 @@
       </c>
       <c r="AX41" s="6">
         <f t="shared" si="18"/>
-        <v>303518</v>
+        <v>303536</v>
       </c>
       <c r="AY41" s="5">
-        <v>816715</v>
+        <v>816733</v>
       </c>
       <c r="AZ41" s="7">
         <f t="shared" si="19"/>
-        <v>0.94094516764922409</v>
+        <v>0.94096590562148819</v>
       </c>
       <c r="BA41" s="5">
         <v>869274</v>
@@ -7745,14 +7745,14 @@
       </c>
       <c r="BC41" s="6">
         <f t="shared" si="20"/>
-        <v>302086</v>
+        <v>302105</v>
       </c>
       <c r="BD41" s="5">
-        <v>822946</v>
+        <v>822965</v>
       </c>
       <c r="BE41" s="7">
         <f t="shared" si="21"/>
-        <v>0.9467049514882534</v>
+        <v>0.94672680880826987</v>
       </c>
       <c r="BF41" s="5">
         <v>986817</v>
@@ -7762,14 +7762,14 @@
       </c>
       <c r="BH41" s="6">
         <f t="shared" si="24"/>
-        <v>395400</v>
+        <v>395420</v>
       </c>
       <c r="BI41" s="5">
-        <v>937217</v>
+        <v>937237</v>
       </c>
       <c r="BJ41" s="7">
         <f t="shared" si="25"/>
-        <v>0.94973738798581697</v>
+        <v>0.94975765516808086</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7974,14 +7974,14 @@
       </c>
       <c r="BH42" s="6">
         <f t="shared" si="24"/>
-        <v>9062</v>
+        <v>9063</v>
       </c>
       <c r="BI42" s="5">
-        <v>19056</v>
+        <v>19057</v>
       </c>
       <c r="BJ42" s="7">
         <f t="shared" si="25"/>
-        <v>0.94038689301223843</v>
+        <v>0.94043624161073824</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8050,14 +8050,14 @@
       </c>
       <c r="T43" s="6">
         <f t="shared" si="6"/>
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="U43" s="5">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="V43" s="7">
         <f t="shared" si="7"/>
-        <v>0.89347496206373289</v>
+        <v>0.8937784522003035</v>
       </c>
       <c r="W43" s="5">
         <v>3265</v>
@@ -8067,14 +8067,14 @@
       </c>
       <c r="Y43" s="6">
         <f t="shared" si="8"/>
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="Z43" s="5">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="AA43" s="7">
         <f t="shared" si="9"/>
-        <v>0.90719754977029099</v>
+        <v>0.90750382848392042</v>
       </c>
       <c r="AB43" s="6">
         <v>4071</v>
@@ -8084,14 +8084,14 @@
       </c>
       <c r="AD43" s="6">
         <f t="shared" si="10"/>
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="AE43" s="5">
-        <v>3743</v>
+        <v>3744</v>
       </c>
       <c r="AF43" s="7">
         <f t="shared" si="11"/>
-        <v>0.91943011545074915</v>
+        <v>0.91967575534266766</v>
       </c>
       <c r="AG43" s="5">
         <v>3330</v>
@@ -8101,14 +8101,14 @@
       </c>
       <c r="AI43" s="6">
         <f t="shared" si="12"/>
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="AK43" s="7">
         <f t="shared" si="13"/>
-        <v>0.90480480480480485</v>
+        <v>0.90510510510510511</v>
       </c>
       <c r="AL43" s="5">
         <v>3339</v>
@@ -8118,14 +8118,14 @@
       </c>
       <c r="AN43" s="6">
         <f t="shared" si="14"/>
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AO43" s="5">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="AP43" s="7">
         <f t="shared" si="15"/>
-        <v>0.90685834082060501</v>
+        <v>0.90715783168613362</v>
       </c>
       <c r="AQ43" s="6">
         <v>4111</v>
@@ -8135,14 +8135,14 @@
       </c>
       <c r="AS43" s="6">
         <f t="shared" si="16"/>
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="AT43" s="5">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="AU43" s="7">
         <f t="shared" si="17"/>
-        <v>0.92848455363658478</v>
+        <v>0.9287278034541474</v>
       </c>
       <c r="AV43" s="5">
         <v>3256</v>
@@ -8152,14 +8152,14 @@
       </c>
       <c r="AX43" s="6">
         <f t="shared" si="18"/>
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="AY43" s="5">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="AZ43" s="7">
         <f t="shared" si="19"/>
-        <v>0.94441031941031939</v>
+        <v>0.94471744471744468</v>
       </c>
       <c r="BA43" s="5">
         <v>3286</v>
@@ -8169,14 +8169,14 @@
       </c>
       <c r="BC43" s="6">
         <f t="shared" si="20"/>
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="BD43" s="5">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="BE43" s="7">
         <f t="shared" si="21"/>
-        <v>0.94339622641509435</v>
+        <v>0.94370054777845402</v>
       </c>
       <c r="BF43" s="5">
         <v>4091</v>
@@ -8186,14 +8186,14 @@
       </c>
       <c r="BH43" s="6">
         <f t="shared" si="24"/>
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="BI43" s="5">
-        <v>3896</v>
+        <v>3897</v>
       </c>
       <c r="BJ43" s="7">
         <f t="shared" si="25"/>
-        <v>0.95233439256905406</v>
+        <v>0.95257883158152046</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8262,14 +8262,14 @@
       </c>
       <c r="T44" s="6">
         <f t="shared" si="6"/>
-        <v>156957</v>
+        <v>156959</v>
       </c>
       <c r="U44" s="5">
-        <v>272186</v>
+        <v>272188</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" si="7"/>
-        <v>0.84405040995298874</v>
+        <v>0.84405661196492143</v>
       </c>
       <c r="W44" s="5">
         <v>327345</v>
@@ -8279,14 +8279,14 @@
       </c>
       <c r="Y44" s="6">
         <f t="shared" si="8"/>
-        <v>161080</v>
+        <v>161081</v>
       </c>
       <c r="Z44" s="5">
-        <v>275337</v>
+        <v>275338</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="9"/>
-        <v>0.84112175227970487</v>
+        <v>0.84112480716064086</v>
       </c>
       <c r="AB44" s="6">
         <v>393681</v>
@@ -8296,14 +8296,14 @@
       </c>
       <c r="AD44" s="6">
         <f t="shared" si="10"/>
-        <v>175096</v>
+        <v>175097</v>
       </c>
       <c r="AE44" s="5">
-        <v>336176</v>
+        <v>336177</v>
       </c>
       <c r="AF44" s="7">
         <f t="shared" si="11"/>
-        <v>0.8539299585197152</v>
+        <v>0.85393249864738197</v>
       </c>
       <c r="AG44" s="5">
         <v>333199</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="AI44" s="6">
         <f t="shared" si="12"/>
-        <v>145825</v>
+        <v>145826</v>
       </c>
       <c r="AJ44" s="5">
-        <v>279563</v>
+        <v>279564</v>
       </c>
       <c r="AK44" s="7">
         <f t="shared" si="13"/>
-        <v>0.83902712793255685</v>
+        <v>0.83903012914204422</v>
       </c>
       <c r="AL44" s="5">
         <v>336893</v>
@@ -8330,14 +8330,14 @@
       </c>
       <c r="AN44" s="6">
         <f t="shared" si="14"/>
-        <v>65083</v>
+        <v>65084</v>
       </c>
       <c r="AO44" s="5">
-        <v>284669</v>
+        <v>284670</v>
       </c>
       <c r="AP44" s="7">
         <f t="shared" si="15"/>
-        <v>0.84498342203607668</v>
+        <v>0.84498639033758494</v>
       </c>
       <c r="AQ44" s="6">
         <v>406157</v>
@@ -8347,14 +8347,14 @@
       </c>
       <c r="AS44" s="6">
         <f t="shared" si="16"/>
-        <v>177445</v>
+        <v>177446</v>
       </c>
       <c r="AT44" s="5">
-        <v>347548</v>
+        <v>347549</v>
       </c>
       <c r="AU44" s="7">
         <f t="shared" si="17"/>
-        <v>0.85569865840056925</v>
+        <v>0.85570112050266278</v>
       </c>
       <c r="AV44" s="5">
         <v>341214</v>
@@ -8364,14 +8364,14 @@
       </c>
       <c r="AX44" s="6">
         <f t="shared" si="18"/>
-        <v>140162</v>
+        <v>140163</v>
       </c>
       <c r="AY44" s="5">
-        <v>288754</v>
+        <v>288755</v>
       </c>
       <c r="AZ44" s="7">
         <f t="shared" si="19"/>
-        <v>0.84625484300175258</v>
+        <v>0.84625777371385702</v>
       </c>
       <c r="BA44" s="5">
         <v>343859</v>
@@ -8381,14 +8381,14 @@
       </c>
       <c r="BC44" s="6">
         <f t="shared" si="20"/>
-        <v>138784</v>
+        <v>138785</v>
       </c>
       <c r="BD44" s="5">
-        <v>292345</v>
+        <v>292346</v>
       </c>
       <c r="BE44" s="7">
         <f t="shared" si="21"/>
-        <v>0.85018859474377584</v>
+        <v>0.85019150291253098</v>
       </c>
       <c r="BF44" s="5">
         <v>410714</v>
@@ -8398,14 +8398,14 @@
       </c>
       <c r="BH44" s="6">
         <f t="shared" si="24"/>
-        <v>190899</v>
+        <v>190900</v>
       </c>
       <c r="BI44" s="5">
-        <v>354698</v>
+        <v>354699</v>
       </c>
       <c r="BJ44" s="7">
         <f t="shared" si="25"/>
-        <v>0.86361312251347655</v>
+        <v>0.86361555729777895</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8474,14 +8474,14 @@
       </c>
       <c r="T45" s="6">
         <f t="shared" si="6"/>
-        <v>110255</v>
+        <v>110256</v>
       </c>
       <c r="U45" s="5">
-        <v>218695</v>
+        <v>218696</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" si="7"/>
-        <v>0.90035364493060899</v>
+        <v>0.90035776186810157</v>
       </c>
       <c r="W45" s="5">
         <v>244806</v>
@@ -8491,14 +8491,14 @@
       </c>
       <c r="Y45" s="6">
         <f t="shared" si="8"/>
-        <v>113532</v>
+        <v>113533</v>
       </c>
       <c r="Z45" s="5">
-        <v>220503</v>
+        <v>220504</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="9"/>
-        <v>0.90072547241489176</v>
+        <v>0.90072955728209281</v>
       </c>
       <c r="AB45" s="6">
         <v>299772</v>
@@ -8508,14 +8508,14 @@
       </c>
       <c r="AD45" s="6">
         <f t="shared" si="10"/>
-        <v>124974</v>
+        <v>124975</v>
       </c>
       <c r="AE45" s="5">
-        <v>271304</v>
+        <v>271305</v>
       </c>
       <c r="AF45" s="7">
         <f t="shared" si="11"/>
-        <v>0.90503449288125637</v>
+        <v>0.90503782874984984</v>
       </c>
       <c r="AG45" s="5">
         <v>246243</v>
@@ -8525,14 +8525,14 @@
       </c>
       <c r="AI45" s="6">
         <f t="shared" si="12"/>
-        <v>101047</v>
+        <v>101048</v>
       </c>
       <c r="AJ45" s="5">
-        <v>222572</v>
+        <v>222573</v>
       </c>
       <c r="AK45" s="7">
         <f t="shared" si="13"/>
-        <v>0.90387137908488768</v>
+        <v>0.90387544011403365</v>
       </c>
       <c r="AL45" s="5">
         <v>247584</v>
@@ -8542,14 +8542,14 @@
       </c>
       <c r="AN45" s="6">
         <f t="shared" si="14"/>
-        <v>40255</v>
+        <v>40256</v>
       </c>
       <c r="AO45" s="5">
-        <v>225202</v>
+        <v>225203</v>
       </c>
       <c r="AP45" s="7">
         <f t="shared" si="15"/>
-        <v>0.90959835853690063</v>
+        <v>0.90960239757011763</v>
       </c>
       <c r="AQ45" s="6">
         <v>303759</v>
@@ -8559,14 +8559,14 @@
       </c>
       <c r="AS45" s="6">
         <f t="shared" si="16"/>
-        <v>134143</v>
+        <v>134145</v>
       </c>
       <c r="AT45" s="5">
-        <v>277036</v>
+        <v>277038</v>
       </c>
       <c r="AU45" s="7">
         <f t="shared" si="17"/>
-        <v>0.91202565191484042</v>
+        <v>0.91203223608189388</v>
       </c>
       <c r="AV45" s="5">
         <v>248547</v>
@@ -8576,14 +8576,14 @@
       </c>
       <c r="AX45" s="6">
         <f t="shared" si="18"/>
-        <v>101079</v>
+        <v>101081</v>
       </c>
       <c r="AY45" s="5">
-        <v>227086</v>
+        <v>227088</v>
       </c>
       <c r="AZ45" s="7">
         <f t="shared" si="19"/>
-        <v>0.91365415796609895</v>
+        <v>0.91366220473391346</v>
       </c>
       <c r="BA45" s="5">
         <v>248925</v>
@@ -8593,14 +8593,14 @@
       </c>
       <c r="BC45" s="6">
         <f t="shared" si="20"/>
-        <v>98872</v>
+        <v>98874</v>
       </c>
       <c r="BD45" s="5">
-        <v>229252</v>
+        <v>229254</v>
       </c>
       <c r="BE45" s="7">
         <f t="shared" si="21"/>
-        <v>0.92096816310133578</v>
+        <v>0.92097619764989458</v>
       </c>
       <c r="BF45" s="5">
         <v>305535</v>
@@ -8610,14 +8610,14 @@
       </c>
       <c r="BH45" s="6">
         <f t="shared" si="24"/>
-        <v>145884</v>
+        <v>145887</v>
       </c>
       <c r="BI45" s="5">
-        <v>281597</v>
+        <v>281600</v>
       </c>
       <c r="BJ45" s="7">
         <f t="shared" si="25"/>
-        <v>0.9216521838741879</v>
+        <v>0.92166200271654641</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9119,15 +9119,15 @@
       </c>
       <c r="T48" s="10">
         <f t="shared" si="6"/>
-        <v>3238937</v>
+        <v>3239007</v>
       </c>
       <c r="U48" s="9">
         <f>SUM(U10:U47)</f>
-        <v>6483994</v>
+        <v>6484064</v>
       </c>
       <c r="V48" s="8">
         <f t="shared" si="7"/>
-        <v>0.92387091442502378</v>
+        <v>0.92388088836454463</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="Y48" s="9">
         <f t="shared" si="8"/>
-        <v>3177302</v>
+        <v>3177377</v>
       </c>
       <c r="Z48" s="9">
         <f>SUM(Z10:Z47)</f>
-        <v>6602923</v>
+        <v>6602998</v>
       </c>
       <c r="AA48" s="8">
         <f t="shared" si="9"/>
-        <v>0.92661419112921106</v>
+        <v>0.92662471617460906</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="AD48" s="10">
         <f t="shared" si="10"/>
-        <v>4486754</v>
+        <v>4486849</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>10492324</v>
+        <v>10492419</v>
       </c>
       <c r="AF48" s="8">
         <f t="shared" si="11"/>
-        <v>0.93839164352807902</v>
+        <v>0.9384001399494758</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="AI48" s="10">
         <f t="shared" si="12"/>
-        <v>2996061</v>
+        <v>2996138</v>
       </c>
       <c r="AJ48" s="9">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6600773</v>
+        <v>6600850</v>
       </c>
       <c r="AK48" s="8">
         <f t="shared" si="13"/>
-        <v>0.92612791976742881</v>
+        <v>0.92613872332783331</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AN48" s="10">
         <f t="shared" si="14"/>
-        <v>1213434</v>
+        <v>1213507</v>
       </c>
       <c r="AO48" s="9">
         <f>SUM(AO10:AO47)</f>
-        <v>6708603</v>
+        <v>6708676</v>
       </c>
       <c r="AP48" s="8">
         <f t="shared" si="15"/>
-        <v>0.93058343918438946</v>
+        <v>0.93059356537475435</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AS48" s="10">
         <f t="shared" si="16"/>
-        <v>4624812</v>
+        <v>4624915</v>
       </c>
       <c r="AT48" s="9">
         <f>SUM(AT10:AT47)</f>
-        <v>10740639</v>
+        <v>10740742</v>
       </c>
       <c r="AU48" s="8">
         <f t="shared" si="17"/>
-        <v>0.93976187290923074</v>
+        <v>0.93977088498690231</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AX48" s="10">
         <f t="shared" si="18"/>
-        <v>2609983</v>
+        <v>2610057</v>
       </c>
       <c r="AY48" s="9">
         <f>SUM(AY10:AY47)</f>
-        <v>6761055</v>
+        <v>6761129</v>
       </c>
       <c r="AZ48" s="8">
         <f t="shared" si="19"/>
-        <v>0.93349074096829854</v>
+        <v>0.93350095805939337</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="BC48" s="10">
         <f t="shared" si="20"/>
-        <v>2559005</v>
+        <v>2559079</v>
       </c>
       <c r="BD48" s="9">
         <f>SUM(BD10:BD47)</f>
-        <v>6870543</v>
+        <v>6870617</v>
       </c>
       <c r="BE48" s="8">
         <f t="shared" ref="BE48" si="26">BD48/BA48</f>
-        <v>0.93965909619324539</v>
+        <v>0.93966921690322691</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="BH48" s="10">
         <f t="shared" si="24"/>
-        <v>4819442</v>
+        <v>4819547</v>
       </c>
       <c r="BI48" s="9">
         <f>SUM(BI10:BI47)</f>
-        <v>10951107</v>
+        <v>10951212</v>
       </c>
       <c r="BJ48" s="8">
         <f t="shared" si="25"/>
-        <v>0.94152799447211277</v>
+        <v>0.94153702191010791</v>
       </c>
     </row>
   </sheetData>
